--- a/product_upload/packages/31/file.xlsx
+++ b/product_upload/packages/31/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>CLARINASE TAB</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-65A35A7EE2A0</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1026,6 +1036,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>OLANA 5 mg orodispersible tablet</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-4483D24600F2</t>
         </is>
       </c>
@@ -1049,7 +1064,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1212,6 +1227,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>DEFIROX 250 mg dispersible tablet</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-9524185D2DD7</t>
         </is>
       </c>
@@ -1235,7 +1255,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1402,6 +1422,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>DEFIROX 500 mg dispersible tablet</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-4223D90A2EB5</t>
         </is>
       </c>
@@ -1425,7 +1450,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1592,6 +1617,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>DIOSTAR 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-71B7D13DF756</t>
         </is>
       </c>
@@ -1615,7 +1645,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1782,6 +1812,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>DIOSTAR 160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-1AC94E4BAA80</t>
         </is>
       </c>
@@ -1805,7 +1840,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1972,6 +2007,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>MOXIVE 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-08092D5109D8</t>
         </is>
       </c>
@@ -1995,7 +2035,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2166,6 +2206,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>MOXIVE 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-B4A7653E6948</t>
         </is>
       </c>
@@ -2189,7 +2234,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2348,6 +2393,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>DEFIROX 125 mg dispersible tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-A2AFBA39A9E5</t>
         </is>
       </c>
@@ -2371,7 +2421,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2542,6 +2592,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>BOOSTRIX VACCINE</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-D592382C92B6</t>
         </is>
       </c>
@@ -2565,7 +2620,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2732,6 +2787,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>ZYMAXID 0.5% eye drops solution</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-A84F954DC758</t>
         </is>
       </c>
@@ -2755,7 +2815,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2918,6 +2978,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Elong 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-C6A557B0F250</t>
         </is>
       </c>
@@ -2941,7 +3006,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3108,6 +3173,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Elong 60 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-2B3CDD3B14FD</t>
         </is>
       </c>
@@ -3131,7 +3201,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3290,6 +3360,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ULTIBRO Breezhaler</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-5CB34F7E3904</t>
         </is>
       </c>
@@ -3313,7 +3388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3484,6 +3559,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>VFEND 200MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-687B425AE4AE</t>
         </is>
       </c>
@@ -3507,7 +3587,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3674,6 +3754,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ALFOSIN XR 10 mg prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-677220FCB9D4</t>
         </is>
       </c>
@@ -3697,7 +3782,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3860,6 +3945,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>TABIXA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-5E956AEA6544</t>
         </is>
       </c>
@@ -3883,7 +3973,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4044,6 +4134,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>HALURAN inhalation solution</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-81DBF5265326</t>
         </is>
       </c>
@@ -4067,7 +4162,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4226,6 +4321,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>LORETA 5mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-EC54F3D48174</t>
         </is>
       </c>
@@ -4249,7 +4349,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4408,6 +4508,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>LORA FM 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-A56BFD8C22A7</t>
         </is>
       </c>
@@ -4431,7 +4536,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4590,6 +4695,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>QUETTA 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-13F109923921</t>
         </is>
       </c>
@@ -4613,7 +4723,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4772,6 +4882,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>QUETTA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-542B9D8C2E99</t>
         </is>
       </c>
@@ -4795,7 +4910,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4962,6 +5077,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>VFEND 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-B82BFBB04CA9</t>
         </is>
       </c>
@@ -4985,7 +5105,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5148,6 +5268,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>QUETTA 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-19BF87C50D44</t>
         </is>
       </c>
@@ -5171,7 +5296,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5330,6 +5455,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>TALOPAM 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-3438CCB7F05D</t>
         </is>
       </c>
@@ -5353,7 +5483,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5516,6 +5646,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>PREZISTA 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-0AC32D5E09F6</t>
         </is>
       </c>
@@ -5539,7 +5674,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5694,6 +5829,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>PREZISTA 600 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-BC1DB836AB31</t>
         </is>
       </c>
@@ -5717,7 +5857,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5880,6 +6020,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>GIOTRIF 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-E4E29D716FF2</t>
         </is>
       </c>
@@ -5903,7 +6048,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6070,6 +6215,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>GIOTRIF 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-168329F19AD8</t>
         </is>
       </c>
@@ -6093,7 +6243,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6248,6 +6398,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>CLOFAST-P 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-977AFF99084A</t>
         </is>
       </c>
@@ -6271,7 +6426,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6438,6 +6593,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>NORMALIX SR 1.5 mg modified-release tablet</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-3403CE94E9EE</t>
         </is>
       </c>
@@ -6461,7 +6621,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6620,6 +6780,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>TALOPAM 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-E8954CF266C5</t>
         </is>
       </c>
@@ -6643,7 +6808,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6796,6 +6961,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-3A142C86D0B5</t>
         </is>
       </c>
@@ -6819,7 +6989,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6978,6 +7148,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>QUETTA 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-C812DF924BD2</t>
         </is>
       </c>
@@ -7001,7 +7176,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7164,6 +7339,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>PANTOL 40 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-813284C44F44</t>
         </is>
       </c>
@@ -7187,7 +7367,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7346,6 +7526,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>ALERSON 0.1 % Cream</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-D07EC2E353D4</t>
         </is>
       </c>
@@ -7369,7 +7554,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7532,6 +7717,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ALERSON 0.1 % Ointment</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-F023CCC421D7</t>
         </is>
       </c>
@@ -7555,7 +7745,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7726,6 +7916,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>HEPAVIR 0.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-BCCBDACCC2A1</t>
         </is>
       </c>
@@ -7749,7 +7944,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7916,6 +8111,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>HEPAVIR 1 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-59E664E0B42A</t>
         </is>
       </c>
@@ -7939,7 +8139,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8102,6 +8302,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-90BE127E112B</t>
         </is>
       </c>
@@ -8125,7 +8330,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8284,6 +8489,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-607F054D1545</t>
         </is>
       </c>
@@ -8307,7 +8517,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8466,6 +8676,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-D564475C5753</t>
         </is>
       </c>
@@ -8489,7 +8704,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8648,6 +8863,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-681967BE2710</t>
         </is>
       </c>
@@ -8671,7 +8891,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8830,6 +9050,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>KIVEXA film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-C987C1E9D202</t>
         </is>
       </c>
@@ -8853,7 +9078,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9030,6 +9255,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>HEXAXIM vaccine</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-3BB852A943A9</t>
         </is>
       </c>
@@ -9053,7 +9283,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9218,6 +9448,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>HEXAXIM vaccine</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-3FCDF7D51263</t>
         </is>
       </c>
@@ -9241,7 +9476,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9410,6 +9645,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>JALRA 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-3889FC6D2ACE</t>
         </is>
       </c>
@@ -9433,7 +9673,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9598,6 +9838,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>JALRA 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-FA21A7330FC9</t>
         </is>
       </c>
@@ -9621,7 +9866,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9790,6 +10035,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>JALRA M</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-80A746D64454</t>
         </is>
       </c>
@@ -9813,7 +10063,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9982,6 +10232,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t xml:space="preserve">JALRA M </t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-7FD0715F92CA</t>
         </is>
       </c>
@@ -10005,7 +10260,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10172,6 +10427,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>PEMAR 10 mg prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-DFE7E669DF00</t>
         </is>
       </c>
@@ -10195,7 +10455,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10354,6 +10614,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>PANTOL 20 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-D4C1B1C96B6C</t>
         </is>
       </c>
@@ -10377,7 +10642,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10548,6 +10813,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ATROSOL 250 mcg/ml nebuliser solution</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-9492ED886086</t>
         </is>
       </c>
@@ -10571,7 +10841,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10734,6 +11004,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>PANTOL 40 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-CC0D566F190F</t>
         </is>
       </c>
@@ -10757,7 +11032,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10920,6 +11195,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>AZAR 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-8DD9CE663F99</t>
         </is>
       </c>
@@ -10943,7 +11223,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11102,6 +11382,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>AZAR 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-8DFDC14D7497</t>
         </is>
       </c>
@@ -11125,7 +11410,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11284,6 +11569,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>AZAR-D 50/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-747F15882FF1</t>
         </is>
       </c>
@@ -11307,7 +11597,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11470,6 +11760,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>AZAR-D 100/25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-B2D83EBC00B9</t>
         </is>
       </c>
@@ -11493,7 +11788,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11652,6 +11947,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>LD-NOR 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-FA7EE2DE3DC8</t>
         </is>
       </c>
@@ -11675,7 +11975,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11834,6 +12134,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>LD-NOR 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-995725909D51</t>
         </is>
       </c>
@@ -11857,7 +12162,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12020,6 +12325,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>LD-NOR 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-36427EF2E960</t>
         </is>
       </c>
@@ -12043,7 +12353,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12214,6 +12524,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>HARVONI 400/90 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-7FBE4C2AA26B</t>
         </is>
       </c>
@@ -12237,7 +12552,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12404,6 +12719,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>HEPATAB 0.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-FAECE0074400</t>
         </is>
       </c>
@@ -12427,7 +12747,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12598,6 +12918,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>HEPATAB 1 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-B1254FDDA40A</t>
         </is>
       </c>
@@ -12621,7 +12946,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12788,6 +13113,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ENTRESTO</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-146A4BC72D20</t>
         </is>
       </c>
@@ -12811,7 +13141,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12982,6 +13312,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ENTRESTO</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-7F48A832E033</t>
         </is>
       </c>
@@ -13005,7 +13340,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13172,6 +13507,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>ENTRESTO 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-B84FAF02E802</t>
         </is>
       </c>
@@ -13195,7 +13535,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13366,6 +13706,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>CLOGREL 75 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-EEE674E33910</t>
         </is>
       </c>
@@ -13389,7 +13734,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13556,6 +13901,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>QUETAL XR 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-35091EE0DD96</t>
         </is>
       </c>
@@ -13579,7 +13929,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13738,6 +14088,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>QUETAL XR 150 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-D147D339A136</t>
         </is>
       </c>
@@ -13761,7 +14116,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13932,6 +14287,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>QUETAL XR 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-6B9B0742E6AD</t>
         </is>
       </c>
@@ -13955,7 +14315,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14118,6 +14478,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>LEVANIX 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-90F923C52A5D</t>
         </is>
       </c>
@@ -14141,7 +14506,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14302,6 +14667,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-E39DE5503F09</t>
         </is>
       </c>
@@ -14325,7 +14695,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14486,6 +14856,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-438C7F71149D</t>
         </is>
       </c>
@@ -14509,7 +14884,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14680,6 +15055,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>VALES 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-6D7324C30CDF</t>
         </is>
       </c>
@@ -14703,7 +15083,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14866,6 +15246,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>VALES 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-F1F7879ADEE9</t>
         </is>
       </c>
@@ -14889,7 +15274,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15056,6 +15441,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>ARTHOSAVE 200 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-88B0DB8C3B42</t>
         </is>
       </c>
@@ -15079,7 +15469,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15250,6 +15640,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>SIRDALUD 2MG TAB</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-12928C7E2335</t>
         </is>
       </c>
@@ -15273,7 +15668,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15444,6 +15839,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>SIRDALUD 4MG TAB</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-7AE457C378E1</t>
         </is>
       </c>
@@ -15467,7 +15867,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15634,6 +16034,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>TRILEPTAL 300MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-85BD829C75FB</t>
         </is>
       </c>
@@ -15657,7 +16062,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15830,6 +16235,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>CATAFLAM 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-6275E6A23760</t>
         </is>
       </c>
@@ -15853,7 +16263,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16016,6 +16426,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>FAMVIR 125MGTAB</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D45E0EB796CC</t>
         </is>
       </c>
@@ -16039,7 +16454,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16206,6 +16621,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>FAMVIR 250MG TAB</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-0580B4B1DEC7</t>
         </is>
       </c>
@@ -16229,7 +16649,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16396,6 +16816,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>TRILEPTAL 600MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-EF87CCEA1979</t>
         </is>
       </c>
@@ -16419,7 +16844,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16590,6 +17015,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>TRILEPTAL 60MG\ML SUSPENTION</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-48A52966826F</t>
         </is>
       </c>
@@ -16613,7 +17043,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16780,6 +17210,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>CATAFAST 50 MG SACHET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-4CC700751594</t>
         </is>
       </c>
@@ -16803,7 +17238,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16970,6 +17405,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>MOSEGOR SYRUP</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-004DC77C8651</t>
         </is>
       </c>
@@ -16993,7 +17433,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17160,6 +17600,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>SANDIMMUN NEORAL DRINK 100MG-ML</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-B075D5682996</t>
         </is>
       </c>
@@ -17183,7 +17628,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17356,6 +17801,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>VOLTAREN 50 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-1F7F8486F543</t>
         </is>
       </c>
@@ -17379,7 +17829,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17546,6 +17996,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>VOLTAREN 100 MG</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-E3FD22D47864</t>
         </is>
       </c>
@@ -17569,7 +18024,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17740,6 +18195,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>VALES 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-F101CB4D0F1C</t>
         </is>
       </c>
@@ -17763,7 +18223,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17934,6 +18394,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>VALES 1000 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-253AF4D1D7C8</t>
         </is>
       </c>
@@ -17957,7 +18422,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18130,6 +18595,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>SANDIMMUN NEORAL 100MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-62144F082932</t>
         </is>
       </c>
@@ -18153,7 +18623,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18316,6 +18786,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>SANDIMMUN NEORAL 50MG CAP</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-25C2922529B9</t>
         </is>
       </c>
@@ -18339,7 +18814,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18510,6 +18985,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>MOSEGOR 0.5MG SUGAR COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-93D66DB5F083</t>
         </is>
       </c>
@@ -18533,7 +19013,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18708,6 +19188,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>PARLODEL 2.5 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-D7486F6624F1</t>
         </is>
       </c>
@@ -18731,7 +19216,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18904,6 +19389,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>VOLTAREN 25 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-A8852654A163</t>
         </is>
       </c>
@@ -18927,7 +19417,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19090,6 +19580,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>VOLTAREN 50 MG. SUPP.</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-0DA8DDE534BB</t>
         </is>
       </c>
@@ -19113,7 +19608,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19288,6 +19783,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>VOLTAREN 75 Mg SR TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-4A5DD9D25235</t>
         </is>
       </c>
@@ -19311,7 +19811,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19477,6 +19977,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>SANDIMMUN NEORAL 25MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-99627CFD2114</t>
         </is>
@@ -19493,7 +19998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19539,100 +20044,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19664,7 +20174,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19679,92 +20189,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-35004</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>113.46</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>253</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19796,7 +20311,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19811,92 +20326,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-52585</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>213.38</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>254</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19928,7 +20448,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19943,92 +20463,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-72131</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>31.52</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>255</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20060,7 +20585,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20075,92 +20600,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-15547</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>288.64</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>256</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20192,7 +20722,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20207,92 +20737,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-10463</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>53.98</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>257</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20324,7 +20859,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20339,92 +20874,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-54841</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>432.06</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>258</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20456,7 +20996,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20471,92 +21011,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-68951</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>174.69</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>259</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20588,7 +21133,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20603,92 +21148,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-34527</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>67.20999999999999</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>260</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20720,7 +21270,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20735,92 +21285,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-81931</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>366.07</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>261</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20852,7 +21407,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20867,92 +21422,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-46342</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>286.01</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>262</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20984,7 +21544,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20999,92 +21559,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-76496</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>416.78</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>263</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21101,7 +21666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21207,6 +21772,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21242,7 +21817,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21307,6 +21882,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-FFFC806E62A9</t>
         </is>
@@ -21343,7 +21928,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21408,6 +21993,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-9750E3F71E96</t>
         </is>
@@ -21444,7 +22039,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21509,6 +22104,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-5060B30D5DAC</t>
         </is>
@@ -21545,7 +22150,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21610,6 +22215,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-8D8F0F5F3687</t>
         </is>
@@ -21646,7 +22261,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21711,6 +22326,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-9422CEBF5464</t>
         </is>
@@ -21747,7 +22372,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21812,6 +22437,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-1BFF19E6BAC9</t>
         </is>
@@ -21848,7 +22483,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21913,6 +22548,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-750261FADED8</t>
         </is>
@@ -21949,7 +22594,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22014,6 +22659,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-71E18DE2CF64</t>
         </is>
@@ -22050,7 +22705,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22115,6 +22770,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-DD1B9C57B035</t>
         </is>
@@ -22151,7 +22816,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22216,6 +22881,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-0ED5C2D9C483</t>
         </is>
@@ -22252,7 +22927,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22317,6 +22992,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-727570FEC940</t>
         </is>
@@ -22353,7 +23038,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22418,6 +23103,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-01AE3CF2F7DA</t>
         </is>
@@ -22454,7 +23149,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22519,6 +23214,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-6FF5D6FCE437</t>
         </is>
@@ -22555,7 +23260,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22620,6 +23325,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-379B352A2268</t>
         </is>
@@ -22656,7 +23371,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22721,6 +23436,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-7477457EA269</t>
         </is>
@@ -22757,7 +23482,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22822,6 +23547,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-A31185919A44</t>
         </is>
@@ -22858,7 +23593,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22923,6 +23658,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-21E92738045F</t>
         </is>
@@ -22959,7 +23704,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23024,6 +23769,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-395D8D81E458</t>
         </is>
@@ -23060,7 +23815,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23125,6 +23880,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-D1061558466D</t>
         </is>
@@ -23161,7 +23926,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23226,6 +23991,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-FC0707C5BF47</t>
         </is>

--- a/product_upload/packages/31/file.xlsx
+++ b/product_upload/packages/31/file.xlsx
@@ -885,8 +885,16 @@
           <t>8798132234-409-372577162619</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLANA 5 mg orodispersible tablet</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OLANA 5 mg orodispersible tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1072,8 +1080,16 @@
           <t>0307435747-500-870592061582</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFIROX 250 mg dispersible tablet</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DEFIROX 250 mg dispersible tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1458,8 +1474,16 @@
           <t>1053593380-900-011699069283</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOSTAR 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DIOSTAR 80 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1653,8 +1677,16 @@
           <t>6499538125-287-105793716085</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOSTAR 160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DIOSTAR 160 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2242,8 +2274,16 @@
           <t>7865111157-370-615903958600</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFIROX 125 mg dispersible tablet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DEFIROX 125 mg dispersible tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2823,8 +2863,16 @@
           <t>5535746743-482-895616871512</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Elong 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Elong 30 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3209,8 +3257,16 @@
           <t>0565959936-196-508117836987</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ULTIBRO Breezhaler</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ULTIBRO Breezhaler detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3790,8 +3846,16 @@
           <t>9913659928-703-877696974579</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TABIXA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TABIXA 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3981,8 +4045,16 @@
           <t>6664373394-854-036994870441</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HALURAN inhalation solution</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>HALURAN inhalation solution detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4170,8 +4242,16 @@
           <t>9569941155-027-676159372077</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORETA 5mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LORETA 5mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4357,8 +4437,16 @@
           <t>1630518767-535-930370524199</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORA FM 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LORA FM 10 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4544,8 +4632,16 @@
           <t>7401337012-598-436639018323</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUETTA 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>QUETTA 25 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4731,8 +4827,16 @@
           <t>0764274370-747-797921129371</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUETTA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>QUETTA 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5113,8 +5217,16 @@
           <t>8601576300-750-383506542803</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUETTA 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>QUETTA 200 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5304,8 +5416,16 @@
           <t>0228205343-076-501928159534</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TALOPAM 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TALOPAM 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5491,8 +5611,16 @@
           <t>5022339337-631-000785399565</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREZISTA 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PREZISTA 400 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5682,8 +5810,16 @@
           <t>7666821746-555-980184698889</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREZISTA 600 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PREZISTA 600 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5865,8 +6001,16 @@
           <t>7901042166-390-617714720211</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GIOTRIF 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>GIOTRIF 30 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6056,8 +6200,16 @@
           <t>4661777692-351-475423481471</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GIOTRIF 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>GIOTRIF 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6251,8 +6403,16 @@
           <t>3882041887-561-439623627727</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOFAST-P 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CLOFAST-P 50 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6629,8 +6789,16 @@
           <t>1002238329-417-244361157293</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TALOPAM 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TALOPAM 25 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6816,8 +6984,16 @@
           <t>1912533556-951-300376370472</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6997,8 +7173,16 @@
           <t>2246266148-378-788015585300</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUETTA 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>QUETTA 300 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7184,8 +7368,16 @@
           <t>3691603103-097-817080007604</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANTOL 40 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PANTOL 40 mg enteric-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7375,8 +7567,16 @@
           <t>0123542236-854-885346371928</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALERSON 0.1 % Cream</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ALERSON 0.1 % Cream detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7562,8 +7762,16 @@
           <t>6325262741-925-360452739130</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALERSON 0.1 % Ointment</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ALERSON 0.1 % Ointment detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8147,8 +8355,16 @@
           <t>0779506463-587-113469388395</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>EVITAR 0.1% gel detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8338,8 +8554,16 @@
           <t>9286432215-678-756046118335</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>EVITAR 0.1% gel detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8525,8 +8749,16 @@
           <t>5836755311-018-183310967768</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>EVITAR 0.1% gel detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8712,8 +8944,16 @@
           <t>2122835229-579-862223728074</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVITAR 0.1% gel</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>EVITAR 0.1% gel detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8899,8 +9139,16 @@
           <t>0817292490-636-624121584320</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KIVEXA film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>KIVEXA film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9291,8 +9539,16 @@
           <t>4100971465-119-701803672909</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEXAXIM vaccine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>HEXAXIM vaccine detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -9681,8 +9937,16 @@
           <t>5703460584-659-605070069080</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JALRA 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>JALRA 50 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -10463,8 +10727,16 @@
           <t>7362493254-377-060151012371</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANTOL 20 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PANTOL 20 mg enteric-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10849,8 +11121,16 @@
           <t>3949450994-400-910083107011</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANTOL 40 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PANTOL 40 mg enteric-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11040,8 +11320,16 @@
           <t>2350626329-595-421634808874</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZAR 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AZAR 50 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11231,8 +11519,16 @@
           <t>7920303215-251-871863592073</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZAR 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AZAR 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11418,8 +11714,16 @@
           <t>1651074026-580-142909260818</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZAR-D 50/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>AZAR-D 50/12.5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11605,8 +11909,16 @@
           <t>0060393417-964-220837122501</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZAR-D 100/25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>AZAR-D 100/25 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11796,8 +12108,16 @@
           <t>4340602955-453-847738713651</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LD-NOR 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>LD-NOR 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11983,8 +12303,16 @@
           <t>4653672143-716-310542944446</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LD-NOR 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>LD-NOR 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12170,8 +12498,16 @@
           <t>0328976744-037-670460797645</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LD-NOR 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>LD-NOR 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -13937,8 +14273,16 @@
           <t>2633933406-224-187686036506</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUETAL XR 150 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>QUETAL XR 150 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14323,8 +14667,16 @@
           <t>1249302753-925-591130298887</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVANIX 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LEVANIX 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14514,8 +14866,16 @@
           <t>4287551177-894-227152655648</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14703,8 +15063,16 @@
           <t>3227584471-337-815820863288</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15091,8 +15459,16 @@
           <t>0029545078-486-834760113052</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALES 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>VALES 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -16271,8 +16647,16 @@
           <t>3891525578-404-560636832747</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FAMVIR 125MGTAB</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>FAMVIR 125MGTAB detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/31/file.xlsx
+++ b/product_upload/packages/31/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22050,7 +22050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22131,40 +22131,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22244,38 +22249,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>63.56</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-FFFC806E62A9</t>
         </is>
@@ -22355,38 +22365,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>235.08</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-9750E3F71E96</t>
         </is>
@@ -22466,38 +22481,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>395.93</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-5060B30D5DAC</t>
         </is>
@@ -22577,38 +22597,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>372.97</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-8D8F0F5F3687</t>
         </is>
@@ -22688,38 +22713,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>193.8</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-9422CEBF5464</t>
         </is>
@@ -22799,38 +22829,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>195.32</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-1BFF19E6BAC9</t>
         </is>
@@ -22910,38 +22945,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>226.59</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-750261FADED8</t>
         </is>
@@ -23021,38 +23061,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>344.05</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-71E18DE2CF64</t>
         </is>
@@ -23132,38 +23177,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>276.54</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-DD1B9C57B035</t>
         </is>
@@ -23243,38 +23293,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>290.2</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-0ED5C2D9C483</t>
         </is>
@@ -23354,38 +23409,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>334.49</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-727570FEC940</t>
         </is>
@@ -23465,38 +23525,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>111.18</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-01AE3CF2F7DA</t>
         </is>
@@ -23576,38 +23641,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>200.55</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-6FF5D6FCE437</t>
         </is>
@@ -23687,38 +23757,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>400.61</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-379B352A2268</t>
         </is>
@@ -23798,38 +23873,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>83.39</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-7477457EA269</t>
         </is>
@@ -23909,38 +23989,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>133.61</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-A31185919A44</t>
         </is>
@@ -24020,38 +24105,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>174.83</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-21E92738045F</t>
         </is>
@@ -24131,38 +24221,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-395D8D81E458</t>
         </is>
@@ -24242,38 +24337,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-D1061558466D</t>
         </is>
@@ -24353,38 +24453,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>89.72</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-FC0707C5BF47</t>
         </is>
